--- a/data/trans_orig/IP07A18-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07A18-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que se riesen de él/ella otros chicos en 2007 (tasa de respuesta: 99,1%)</t>
+          <t>Menores según la frecuencia de que se riesen de él/ella otros/as chicos/as, percibida por el adulto en 2007 (tasa de respuesta: 99,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>4081</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>656</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5370</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7289</t>
+          <t>7454</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,47 +880,47 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5331</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>4,93%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>12,95%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>2555</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
           <t>648</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>5472</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>4,93%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>13,3%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>2555</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>653</t>
-        </is>
-      </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6341</t>
+          <t>5859</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>799</t>
+          <t>693</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6914</t>
+          <t>7210</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>693</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7725</t>
+          <t>7023</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>4589</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13083</t>
+          <t>12993</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7965</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7661</t>
+          <t>7687</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18117</t>
+          <t>18391</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>29195</t>
+          <t>29566</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>39352</t>
+          <t>39272</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>28861</t>
+          <t>29082</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>36831</t>
+          <t>37309</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>61127</t>
+          <t>60403</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>73688</t>
+          <t>73551</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>82,89%</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>3962</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3584</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>673</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5719</t>
+          <t>5516</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>5690</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7908</t>
+          <t>8020</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3488</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4275</t>
+          <t>3801</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>5098</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>4315</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12705</t>
+          <t>12283</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>478</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5083</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5632</t>
+          <t>5729</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15288</t>
+          <t>15239</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,0%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14493</t>
+          <t>14152</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23423</t>
+          <t>23137</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21610</t>
+          <t>21756</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28527</t>
+          <t>28808</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>39257</t>
+          <t>38878</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>49936</t>
+          <t>50118</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>82,21%</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4634</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5256</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>672</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>5791</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6902</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>717</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6485</t>
+          <t>6101</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10478</t>
+          <t>10676</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,39%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8853</t>
+          <t>8552</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5404</t>
+          <t>5484</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14051</t>
+          <t>13983</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8861</t>
+          <t>8868</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19591</t>
+          <t>19419</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18569</t>
+          <t>19107</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>27332</t>
+          <t>27135</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35055</t>
+          <t>35704</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>45140</t>
+          <t>45350</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>57568</t>
+          <t>57228</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>70183</t>
+          <t>70492</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,8%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7826</t>
+          <t>8206</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1871</t>
+          <t>2226</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8775</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>4727</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14204</t>
+          <t>13532</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9183</t>
+          <t>9566</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3542</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>11800</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1894</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8317</t>
+          <t>7944</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6799</t>
+          <t>6269</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3317</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11884</t>
+          <t>11828</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>4557</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13489</t>
+          <t>13700</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6682</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16591</t>
+          <t>16251</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12676</t>
+          <t>13359</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>26135</t>
+          <t>27510</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>59661</t>
+          <t>59681</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>72845</t>
+          <t>72592</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>67079</t>
+          <t>67600</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>79679</t>
+          <t>79874</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>132321</t>
+          <t>131060</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>149027</t>
+          <t>149617</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,39%</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3675</t>
+          <t>3369</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7528</t>
+          <t>7006</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1384</t>
+          <t>1370</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7895</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>621</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>678</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5933</t>
+          <t>6066</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>8540</t>
+          <t>9116</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7236</t>
+          <t>7856</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>599</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>5757</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2750</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>10358</t>
+          <t>10482</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>5042</t>
+          <t>5377</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>13907</t>
+          <t>14298</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12884</t>
+          <t>13269</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>11567</t>
+          <t>11191</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>23561</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,86%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>32965</t>
+          <t>32751</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>43683</t>
+          <t>43384</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>47655</t>
+          <t>47951</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>58684</t>
+          <t>59094</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>84254</t>
+          <t>84500</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>100142</t>
+          <t>100169</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,85%</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>3328</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3580</t>
+          <t>3359</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>2724</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3824</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>540</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>4822</t>
+          <t>5165</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3225</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4886</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>638</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5333</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6939</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1353</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>7899</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3833</t>
+          <t>3874</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>11852</t>
+          <t>11762</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>33327</t>
+          <t>33176</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>39948</t>
+          <t>39823</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>24498</t>
+          <t>24067</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>31993</t>
+          <t>31898</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>60329</t>
+          <t>60742</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>70487</t>
+          <t>70227</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,45%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2574</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>10822</t>
+          <t>10587</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>7242</t>
+          <t>6504</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>19036</t>
+          <t>17787</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>11542</t>
+          <t>11415</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>25573</t>
+          <t>24659</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>6532</t>
+          <t>6556</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>17020</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>6290</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>16578</t>
+          <t>16932</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>15349</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>29898</t>
+          <t>30106</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>9783</t>
+          <t>10126</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>22825</t>
+          <t>23243</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>5866</t>
+          <t>5929</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>16324</t>
+          <t>15949</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>18045</t>
+          <t>18373</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>33398</t>
+          <t>33669</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>31577</t>
+          <t>32844</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>51555</t>
+          <t>53144</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>29196</t>
+          <t>29350</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>48226</t>
+          <t>48083</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>65668</t>
+          <t>66204</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>92426</t>
+          <t>91984</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>208282</t>
+          <t>206676</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>232385</t>
+          <t>231978</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>243670</t>
+          <t>243182</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>267700</t>
+          <t>268149</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>459060</t>
+          <t>460197</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>493002</t>
+          <t>493245</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,68%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que se riesen de él/ella otros chicos en 2012 (tasa de respuesta: 97,91%)</t>
+          <t>Menores según la frecuencia de que se riesen de él/ella otros/as chicos/as, percibida por el adulto en 2012 (tasa de respuesta: 97,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>760</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>7238</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12477</t>
+          <t>12364</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,62%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>605</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5567</t>
+          <t>5652</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>720</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2265</t>
+          <t>2063</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9737</t>
+          <t>9264</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7219</t>
+          <t>7126</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>577</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6073</t>
+          <t>5545</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2804</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10778</t>
+          <t>10825</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -6079,12 +6079,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>2823</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10475</t>
+          <t>11036</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6094,12 +6094,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>709</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6240</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14664</t>
+          <t>14179</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,06%</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19681</t>
+          <t>18842</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29947</t>
+          <t>29172</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18340</t>
+          <t>17773</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27151</t>
+          <t>26933</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39656</t>
+          <t>39345</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>54708</t>
+          <t>54070</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>72,68%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>766</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6380</t>
+          <t>6672</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6774</t>
+          <t>7335</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3353</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11461</t>
+          <t>11056</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>15,84%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>2209</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9227</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>577</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6784</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4031</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12641</t>
+          <t>12204</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -6653,7 +6653,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>5745</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2108</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8806</t>
+          <t>9146</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>3565</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11386</t>
+          <t>11639</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -6761,12 +6761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1957</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7882</t>
+          <t>8829</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>1833</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7945</t>
+          <t>7766</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4665</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13877</t>
+          <t>13700</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -6874,12 +6874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15919</t>
+          <t>15344</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25267</t>
+          <t>25193</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6889,49 +6889,49 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>72,58%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>20929</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>16041</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>25551</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>59,62%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>45,7%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>72,79%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>20929</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>15504</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>25394</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>59,62%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>44,17%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>72,34%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>61</t>
@@ -6944,12 +6944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34246</t>
+          <t>34729</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47238</t>
+          <t>47252</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,68%</t>
         </is>
       </c>
     </row>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>4810</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>631</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5240</t>
+          <t>5628</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7288</t>
+          <t>7434</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2066</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8688</t>
+          <t>8793</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1438</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7323</t>
+          <t>7973</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4778</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14080</t>
+          <t>14119</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,5%</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>4497</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12765</t>
+          <t>13347</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7884</t>
+          <t>8077</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>7434</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18596</t>
+          <t>18023</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>23,61%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11035</t>
+          <t>10724</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7478,12 +7478,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>6970</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5649</t>
+          <t>5572</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15235</t>
+          <t>15265</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,0%</t>
         </is>
       </c>
     </row>
@@ -7556,12 +7556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18059</t>
+          <t>17923</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29549</t>
+          <t>29451</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7571,12 +7571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14215</t>
+          <t>13996</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22709</t>
+          <t>22737</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>35853</t>
+          <t>34835</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>49980</t>
+          <t>48774</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>63,9%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5166</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14678</t>
+          <t>13751</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3797</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12304</t>
+          <t>12727</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10471</t>
+          <t>9761</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22639</t>
+          <t>22769</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5835</t>
+          <t>5596</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15817</t>
+          <t>16034</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>5738</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>15666</t>
+          <t>16928</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>13036</t>
+          <t>14010</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>27567</t>
+          <t>28877</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>15,44%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>893</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6140</t>
+          <t>6458</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7323</t>
+          <t>6656</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18386</t>
+          <t>18158</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8781</t>
+          <t>9223</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>21301</t>
+          <t>20694</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3096</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11774</t>
+          <t>11803</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4499</t>
+          <t>4591</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13771</t>
+          <t>13464</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9136</t>
+          <t>9632</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21488</t>
+          <t>22228</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>51477</t>
+          <t>51968</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>65953</t>
+          <t>65947</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>55034</t>
+          <t>54223</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>70814</t>
+          <t>70947</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>111465</t>
+          <t>109754</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>133688</t>
+          <t>131741</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>70,45%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2668</t>
+          <t>2576</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9848</t>
+          <t>10737</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>3290</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10789</t>
+          <t>11190</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7327</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>17851</t>
+          <t>18450</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,57%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>3389</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11093</t>
+          <t>11854</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2745</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10692</t>
+          <t>10300</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7282</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>18487</t>
+          <t>18623</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2807</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10853</t>
+          <t>10447</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9195</t>
+          <t>9252</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6255</t>
+          <t>6129</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>17393</t>
+          <t>16690</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -8807,12 +8807,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>7917</t>
+          <t>7648</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>18712</t>
+          <t>18132</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8822,12 +8822,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>16874</t>
+          <t>17346</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>17680</t>
+          <t>17741</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>31379</t>
+          <t>33203</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>22,63%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>37539</t>
+          <t>37836</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>51261</t>
+          <t>51711</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>36302</t>
+          <t>36946</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>50207</t>
+          <t>50113</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>78657</t>
+          <t>77706</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>97794</t>
+          <t>97793</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>779</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>6987</t>
+          <t>6684</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6125</t>
+          <t>6627</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>10993</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,81%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>754</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>5939</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1310</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>6762</t>
+          <t>7224</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>2832</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>10994</t>
+          <t>11084</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,96%</t>
         </is>
       </c>
     </row>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3902</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9524,12 +9524,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>8059</t>
+          <t>7382</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9539,12 +9539,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>9701</t>
+          <t>9919</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>13297</t>
+          <t>13278</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>21156</t>
+          <t>21007</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -9617,12 +9617,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -9637,12 +9637,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>22076</t>
+          <t>21724</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>30933</t>
+          <t>30344</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>37572</t>
+          <t>37793</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>49216</t>
+          <t>49662</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>80,47%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>15174</t>
+          <t>15268</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>29865</t>
+          <t>31045</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>15184</t>
+          <t>15900</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>30396</t>
+          <t>30843</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>34898</t>
+          <t>34708</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>55705</t>
+          <t>55136</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>23610</t>
+          <t>24288</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>40978</t>
+          <t>41400</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>21039</t>
+          <t>20982</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>36677</t>
+          <t>36975</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>47254</t>
+          <t>48684</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>72704</t>
+          <t>73676</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,96%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>17835</t>
+          <t>17845</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>35358</t>
+          <t>33351</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>23191</t>
+          <t>22641</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>40620</t>
+          <t>40076</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>45399</t>
+          <t>45318</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>68049</t>
+          <t>67856</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>28028</t>
+          <t>28325</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>47373</t>
+          <t>46877</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>25611</t>
+          <t>25700</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>44173</t>
+          <t>43568</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>59195</t>
+          <t>59799</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>85210</t>
+          <t>85119</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>175333</t>
+          <t>176701</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>206033</t>
+          <t>203430</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>181525</t>
+          <t>179979</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>208150</t>
+          <t>208626</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>366642</t>
+          <t>366209</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>405727</t>
+          <t>406275</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>65,96%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que se riesen de él/ella otros chicos en 2016 (tasa de respuesta: 98,52%)</t>
+          <t>Menores según la frecuencia de que se riesen de él/ella otros/as chicos/as, percibida por el adulto en 2016 (tasa de respuesta: 98,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>631</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>5624</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7245</t>
+          <t>7793</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2473</t>
+          <t>2733</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10289</t>
+          <t>10647</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,6%</t>
         </is>
       </c>
     </row>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3408</t>
+          <t>3628</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>904</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>8007</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>8373</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>626</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5927</t>
+          <t>5707</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>4026</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11029,7 +11029,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1730</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7325</t>
+          <t>7591</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2166</t>
+          <t>2169</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9378</t>
+          <t>9164</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>2577</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9633</t>
+          <t>9235</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>6002</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16360</t>
+          <t>15862</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>21,76%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19904</t>
+          <t>19539</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28520</t>
+          <t>28308</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>56,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20183</t>
+          <t>20186</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29710</t>
+          <t>29501</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,71%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>42149</t>
+          <t>42256</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55128</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,61%</t>
         </is>
       </c>
     </row>
@@ -11435,7 +11435,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>3337</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11450,7 +11450,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11470,7 +11470,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11485,7 +11485,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4274</t>
+          <t>5572</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>3375</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11992</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5333</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>4912</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14470</t>
+          <t>15096</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>15,07%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9938</t>
+          <t>10493</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2204</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9684</t>
+          <t>9232</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>5792</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16401</t>
+          <t>16009</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13811</t>
+          <t>14111</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>2985</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11847</t>
+          <t>11848</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10062</t>
+          <t>10111</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22526</t>
+          <t>22327</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24591</t>
+          <t>24387</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36466</t>
+          <t>36232</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27751</t>
+          <t>27601</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38223</t>
+          <t>37774</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>55353</t>
+          <t>55460</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>71307</t>
+          <t>71145</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>71,0%</t>
         </is>
       </c>
     </row>
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>606</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5427</t>
+          <t>5219</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>611</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5268</t>
+          <t>5713</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7077</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1363</t>
+          <t>1394</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7329</t>
+          <t>7380</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>3466</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11890</t>
+          <t>11762</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -12343,7 +12343,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5633</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12358,7 +12358,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>641</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6193</t>
+          <t>6085</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8196</t>
+          <t>9518</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>13,77%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>628</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12486,12 +12486,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3196</t>
+          <t>2724</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10702</t>
+          <t>10457</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4708</t>
+          <t>4513</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13553</t>
+          <t>13455</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,47%</t>
         </is>
       </c>
     </row>
@@ -12564,12 +12564,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15790</t>
+          <t>16209</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24119</t>
+          <t>24136</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12579,12 +12579,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,19%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12599,12 +12599,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21386</t>
+          <t>21442</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31522</t>
+          <t>31488</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>41456</t>
+          <t>41131</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>53671</t>
+          <t>53468</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,37%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>694</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6333</t>
+          <t>5978</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3196</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>12763</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5538</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15525</t>
+          <t>16254</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>3247</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11360</t>
+          <t>11374</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4757</t>
+          <t>4528</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>13373</t>
+          <t>13851</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>9711</t>
+          <t>9369</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>21341</t>
+          <t>21554</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5741</t>
+          <t>5474</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16370</t>
+          <t>16338</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>13077</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11460</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>25391</t>
+          <t>25911</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6605</t>
+          <t>6734</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17777</t>
+          <t>18018</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5354</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15638</t>
+          <t>15385</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13183,12 +13183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13998</t>
+          <t>14765</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28905</t>
+          <t>28567</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>76530</t>
+          <t>76635</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>92246</t>
+          <t>92169</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>61685</t>
+          <t>61186</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>77869</t>
+          <t>76873</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>75,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>144290</t>
+          <t>143489</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>165808</t>
+          <t>166216</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,46%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3057</t>
+          <t>2866</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11640</t>
+          <t>11688</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9099</t>
+          <t>8813</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5972</t>
+          <t>6472</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>16802</t>
+          <t>17138</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2532</t>
+          <t>2188</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10255</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1569</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9233</t>
+          <t>9027</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15898</t>
+          <t>15377</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>6537</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>4921</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14541</t>
+          <t>13792</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>17910</t>
+          <t>17340</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>9590</t>
+          <t>9525</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3497</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12570</t>
+          <t>13019</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7623</t>
+          <t>7948</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>19148</t>
+          <t>18927</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>49183</t>
+          <t>48495</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>61789</t>
+          <t>61710</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>40611</t>
+          <t>40940</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>54148</t>
+          <t>54557</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>93928</t>
+          <t>94032</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>112246</t>
+          <t>112058</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,66%</t>
         </is>
       </c>
     </row>
@@ -14163,7 +14163,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3684</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>669</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5406</t>
+          <t>5646</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>691</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>690</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5921</t>
+          <t>5929</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>714</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6534</t>
+          <t>6336</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2093</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>9618</t>
+          <t>9478</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>597</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4980</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8920</t>
+          <t>9693</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3291</t>
+          <t>3386</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>11661</t>
+          <t>12015</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>
@@ -14497,12 +14497,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2957</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>11042</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14512,12 +14512,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14532,12 +14532,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1413</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>7825</t>
+          <t>7261</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>5366</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>14812</t>
+          <t>15950</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -14610,12 +14610,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>15998</t>
+          <t>16798</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>25490</t>
+          <t>25699</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14625,12 +14625,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14645,12 +14645,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>20048</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>29794</t>
+          <t>30279</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14660,12 +14660,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>40421</t>
+          <t>39623</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>53631</t>
+          <t>52741</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14695,12 +14695,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>74,44%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>7585</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>18584</t>
+          <t>19626</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>13449</t>
+          <t>13142</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>27585</t>
+          <t>27852</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>24298</t>
+          <t>23741</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>41942</t>
+          <t>42673</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>17454</t>
+          <t>18011</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>33518</t>
+          <t>34257</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>17234</t>
+          <t>16701</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>32310</t>
+          <t>32466</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>39060</t>
+          <t>39473</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>61767</t>
+          <t>63150</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>17604</t>
+          <t>16944</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>34420</t>
+          <t>33256</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>21927</t>
+          <t>21776</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>40698</t>
+          <t>38384</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>42586</t>
+          <t>43512</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>66334</t>
+          <t>66212</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15151,12 +15151,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>28851</t>
+          <t>29424</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>48352</t>
+          <t>48906</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>30161</t>
+          <t>30428</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>48584</t>
+          <t>50028</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>64013</t>
+          <t>63270</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>91277</t>
+          <t>91161</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>224800</t>
+          <t>222619</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>251021</t>
+          <t>251725</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,53%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>214454</t>
+          <t>213649</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>243118</t>
+          <t>243081</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>446033</t>
+          <t>446805</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>486322</t>
+          <t>488065</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15377,12 +15377,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,92%</t>
         </is>
       </c>
     </row>
